--- a/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SwdlSecureLib_20260917.xlsx
+++ b/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SwdlSecureLib_20260917.xlsx
@@ -4228,7 +4228,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4268,6 +4268,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4896,7 +4902,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="8" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="8" applyBorder="1"/>
@@ -5381,6 +5387,17 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="0" borderId="0" xfId="0"/>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="56" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="56" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="56" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fillId="8" applyFill="1" numFmtId="0" fontId="56" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Normal 2 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -8341,134 +8358,134 @@
       </c>
     </row>
     <row r="13" spans="1:34">
-      <c r="A13" s="87"/>
-      <c r="B13" s="81" t="str">
+      <c r="A13" s="180"/>
+      <c r="B13" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C13" s="82"/>
-      <c r="D13" s="81" t="inlineStr">
+      <c r="C13" s="178"/>
+      <c r="D13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SRA-SECURITY-SWDL-003</t>
         </is>
       </c>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81" t="inlineStr">
+      <c r="E13" s="177"/>
+      <c r="F13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SWDL-004</t>
         </is>
       </c>
-      <c r="G13" s="81" t="inlineStr">
+      <c r="G13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWDL Secure Lib</t>
         </is>
       </c>
-      <c r="H13" s="81" t="inlineStr">
+      <c r="H13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Package Decryption</t>
         </is>
       </c>
-      <c r="I13" s="81" t="inlineStr">
+      <c r="I13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">.
 (decryption interface handles an input parameter at the range boundary)</t>
         </is>
       </c>
-      <c r="J13" s="81" t="inlineStr">
+      <c r="J13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. An encrypted software package is available</t>
         </is>
       </c>
-      <c r="K13" s="81" t="inlineStr">
+      <c r="K13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L13" s="81" t="inlineStr">
+      <c r="L13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;SWDL decryption test entry point provided by RD (X-l)&gt; is executed
 $ &lt;command provided by RD (X-l)&gt;</t>
         </is>
       </c>
-      <c r="M13" s="81" t="inlineStr">
+      <c r="M13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;SWDL decryption test entry point provided by RD (X-l)&gt;</t>
         </is>
       </c>
-      <c r="N13" s="81" t="inlineStr">
+      <c r="N13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-003</t>
         </is>
       </c>
-      <c r="O13" s="81" t="inlineStr">
+      <c r="O13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P13" s="81" t="inlineStr">
+      <c r="P13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="Q13" s="81"/>
-      <c r="R13" s="81" t="inlineStr">
+      <c r="Q13" s="177"/>
+      <c r="R13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">功能測試 (Functional based ; no specific technique)</t>
         </is>
       </c>
-      <c r="S13" s="81" t="inlineStr">
+      <c r="S13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T13" s="81" t="inlineStr">
+      <c r="T13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U13" s="81" t="inlineStr">
+      <c r="U13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V13" s="81" t="inlineStr">
+      <c r="V13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W13" s="81" t="inlineStr">
+      <c r="W13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X13" s="83" t="inlineStr">
+      <c r="X13" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y13" s="81" t="inlineStr">
+      <c r="Y13" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z13" s="83" t="inlineStr">
+      <c r="Z13" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA13" s="83" t="inlineStr">
+      <c r="AA13" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB13" s="81"/>
-      <c r="AC13" s="81"/>
-      <c r="AD13" s="81"/>
-      <c r="AE13" s="81"/>
-      <c r="AF13" s="81"/>
-      <c r="AG13" s="81"/>
-      <c r="AH13" s="83" t="inlineStr">
+      <c r="AB13" s="177"/>
+      <c r="AC13" s="177"/>
+      <c r="AD13" s="177"/>
+      <c r="AE13" s="177"/>
+      <c r="AF13" s="177"/>
+      <c r="AG13" s="177"/>
+      <c r="AH13" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SRA-SECURITY-SWDL-003 Requirement Description and Verification Criteria
 sibling axis: input range; rule 1 of SEC-04 4.2
@@ -8480,134 +8497,134 @@
       </c>
     </row>
     <row r="14" spans="1:34">
-      <c r="A14" s="87"/>
-      <c r="B14" s="81" t="str">
+      <c r="A14" s="180"/>
+      <c r="B14" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C14" s="82"/>
-      <c r="D14" s="81" t="inlineStr">
+      <c r="C14" s="178"/>
+      <c r="D14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SRA-SECURITY-SWDL-003</t>
         </is>
       </c>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81" t="inlineStr">
+      <c r="E14" s="177"/>
+      <c r="F14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SWDL-005</t>
         </is>
       </c>
-      <c r="G14" s="81" t="inlineStr">
+      <c r="G14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWDL Secure Lib</t>
         </is>
       </c>
-      <c r="H14" s="81" t="inlineStr">
+      <c r="H14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Package Decryption</t>
         </is>
       </c>
-      <c r="I14" s="81" t="inlineStr">
+      <c r="I14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">.
 (decryption of a valid package succeeds)</t>
         </is>
       </c>
-      <c r="J14" s="81" t="inlineStr">
+      <c r="J14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. An encrypted software package is available</t>
         </is>
       </c>
-      <c r="K14" s="81" t="inlineStr">
+      <c r="K14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L14" s="81" t="inlineStr">
+      <c r="L14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;SWDL decryption test entry point provided by RD (X-l)&gt; is executed
 $ &lt;command provided by RD (X-l)&gt;</t>
         </is>
       </c>
-      <c r="M14" s="81" t="inlineStr">
+      <c r="M14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;SWDL decryption test entry point provided by RD (X-l)&gt;</t>
         </is>
       </c>
-      <c r="N14" s="81" t="inlineStr">
+      <c r="N14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-003</t>
         </is>
       </c>
-      <c r="O14" s="81" t="inlineStr">
+      <c r="O14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P14" s="81" t="inlineStr">
+      <c r="P14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="Q14" s="81"/>
-      <c r="R14" s="81" t="inlineStr">
+      <c r="Q14" s="177"/>
+      <c r="R14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">功能測試 (Functional based ; no specific technique)</t>
         </is>
       </c>
-      <c r="S14" s="81" t="inlineStr">
+      <c r="S14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T14" s="81" t="inlineStr">
+      <c r="T14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U14" s="81" t="inlineStr">
+      <c r="U14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V14" s="81" t="inlineStr">
+      <c r="V14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W14" s="81" t="inlineStr">
+      <c r="W14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X14" s="83" t="inlineStr">
+      <c r="X14" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y14" s="81" t="inlineStr">
+      <c r="Y14" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z14" s="83" t="inlineStr">
+      <c r="Z14" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA14" s="83" t="inlineStr">
+      <c r="AA14" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB14" s="81"/>
-      <c r="AC14" s="81"/>
-      <c r="AD14" s="81"/>
-      <c r="AE14" s="81"/>
-      <c r="AF14" s="81"/>
-      <c r="AG14" s="81"/>
-      <c r="AH14" s="83" t="inlineStr">
+      <c r="AB14" s="177"/>
+      <c r="AC14" s="177"/>
+      <c r="AD14" s="177"/>
+      <c r="AE14" s="177"/>
+      <c r="AF14" s="177"/>
+      <c r="AG14" s="177"/>
+      <c r="AH14" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SRA-SECURITY-SWDL-003 Requirement Description and Verification Criteria
 sibling axis: decryption outcome; rule 1,3 of SEC-04 4.2
@@ -8619,134 +8636,134 @@
       </c>
     </row>
     <row r="15" spans="1:34">
-      <c r="A15" s="87"/>
-      <c r="B15" s="81" t="str">
+      <c r="A15" s="180"/>
+      <c r="B15" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C15" s="82"/>
-      <c r="D15" s="81" t="inlineStr">
+      <c r="C15" s="178"/>
+      <c r="D15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SRA-SECURITY-SWDL-003</t>
         </is>
       </c>
-      <c r="E15" s="81"/>
-      <c r="F15" s="81" t="inlineStr">
+      <c r="E15" s="177"/>
+      <c r="F15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SWDL-006</t>
         </is>
       </c>
-      <c r="G15" s="81" t="inlineStr">
+      <c r="G15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWDL Secure Lib</t>
         </is>
       </c>
-      <c r="H15" s="81" t="inlineStr">
+      <c r="H15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Package Decryption</t>
         </is>
       </c>
-      <c r="I15" s="81" t="inlineStr">
+      <c r="I15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">.
 (decryption of an invalid package fails)</t>
         </is>
       </c>
-      <c r="J15" s="81" t="inlineStr">
+      <c r="J15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. An encrypted software package is available</t>
         </is>
       </c>
-      <c r="K15" s="81" t="inlineStr">
+      <c r="K15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L15" s="81" t="inlineStr">
+      <c r="L15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;SWDL decryption test entry point provided by RD (X-l)&gt; is executed
 $ &lt;command provided by RD (X-l)&gt;</t>
         </is>
       </c>
-      <c r="M15" s="81" t="inlineStr">
+      <c r="M15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;SWDL decryption test entry point provided by RD (X-l)&gt;</t>
         </is>
       </c>
-      <c r="N15" s="81" t="inlineStr">
+      <c r="N15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-003</t>
         </is>
       </c>
-      <c r="O15" s="81" t="inlineStr">
+      <c r="O15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P15" s="81" t="inlineStr">
+      <c r="P15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="Q15" s="81"/>
-      <c r="R15" s="81" t="inlineStr">
+      <c r="Q15" s="177"/>
+      <c r="R15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">負向測試 (Negative / Invalid)</t>
         </is>
       </c>
-      <c r="S15" s="81" t="inlineStr">
+      <c r="S15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T15" s="81" t="inlineStr">
+      <c r="T15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U15" s="81" t="inlineStr">
+      <c r="U15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V15" s="81" t="inlineStr">
+      <c r="V15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W15" s="81" t="inlineStr">
+      <c r="W15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X15" s="83" t="inlineStr">
+      <c r="X15" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y15" s="81" t="inlineStr">
+      <c r="Y15" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z15" s="83" t="inlineStr">
+      <c r="Z15" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA15" s="83" t="inlineStr">
+      <c r="AA15" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB15" s="81"/>
-      <c r="AC15" s="81"/>
-      <c r="AD15" s="81"/>
-      <c r="AE15" s="81"/>
-      <c r="AF15" s="81"/>
-      <c r="AG15" s="81"/>
-      <c r="AH15" s="83" t="inlineStr">
+      <c r="AB15" s="177"/>
+      <c r="AC15" s="177"/>
+      <c r="AD15" s="177"/>
+      <c r="AE15" s="177"/>
+      <c r="AF15" s="177"/>
+      <c r="AG15" s="177"/>
+      <c r="AH15" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SRA-SECURITY-SWDL-003 Requirement Description and Verification Criteria
 sibling axis: decryption outcome; rule 1,3 of SEC-04 4.2
@@ -8758,134 +8775,134 @@
       </c>
     </row>
     <row r="16" spans="1:34">
-      <c r="A16" s="87"/>
-      <c r="B16" s="81" t="str">
+      <c r="A16" s="180"/>
+      <c r="B16" s="177" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C16" s="82"/>
-      <c r="D16" s="81" t="inlineStr">
+      <c r="C16" s="178"/>
+      <c r="D16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1-SRA-SECURITY-SWDL-004</t>
         </is>
       </c>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81" t="inlineStr">
+      <c r="E16" s="177"/>
+      <c r="F16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NR1L-SWDL-007</t>
         </is>
       </c>
-      <c r="G16" s="81" t="inlineStr">
+      <c r="G16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWDL Secure Lib</t>
         </is>
       </c>
-      <c r="H16" s="81" t="inlineStr">
+      <c r="H16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">Signature Verification</t>
         </is>
       </c>
-      <c r="I16" s="81" t="inlineStr">
+      <c r="I16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">.
 (verification interface handles an input parameter at the range boundary)</t>
         </is>
       </c>
-      <c r="J16" s="81" t="inlineStr">
+      <c r="J16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. DUT is connected via ADB with root permission (Dev/Eng build)
 2. A signed software package is available</t>
         </is>
       </c>
-      <c r="K16" s="81" t="inlineStr">
+      <c r="K16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NA</t>
         </is>
       </c>
-      <c r="L16" s="81" t="inlineStr">
+      <c r="L16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;SWDL verification test entry point provided by RD (X-l)&gt; is executed
 $ &lt;command provided by RD (X-l)&gt;</t>
         </is>
       </c>
-      <c r="M16" s="81" t="inlineStr">
+      <c r="M16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1. &lt;SWDL verification test entry point provided by RD (X-l)&gt;</t>
         </is>
       </c>
-      <c r="N16" s="81" t="inlineStr">
+      <c r="N16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-004</t>
         </is>
       </c>
-      <c r="O16" s="81" t="inlineStr">
+      <c r="O16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW</t>
         </is>
       </c>
-      <c r="P16" s="81" t="inlineStr">
+      <c r="P16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="81" t="inlineStr">
+      <c r="Q16" s="177"/>
+      <c r="R16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">功能測試 (Functional based ; no specific technique)</t>
         </is>
       </c>
-      <c r="S16" s="81" t="inlineStr">
+      <c r="S16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="T16" s="81" t="inlineStr">
+      <c r="T16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="U16" s="81" t="inlineStr">
+      <c r="U16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="V16" s="81" t="inlineStr">
+      <c r="V16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="W16" s="81" t="inlineStr">
+      <c r="W16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="X16" s="83" t="inlineStr">
+      <c r="X16" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="Y16" s="81" t="inlineStr">
+      <c r="Y16" s="177" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="Z16" s="83" t="inlineStr">
+      <c r="Z16" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="AA16" s="83" t="inlineStr">
+      <c r="AA16" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">PeiPYHsu</t>
         </is>
       </c>
-      <c r="AB16" s="81"/>
-      <c r="AC16" s="81"/>
-      <c r="AD16" s="81"/>
-      <c r="AE16" s="81"/>
-      <c r="AF16" s="81"/>
-      <c r="AG16" s="81"/>
-      <c r="AH16" s="83" t="inlineStr">
+      <c r="AB16" s="177"/>
+      <c r="AC16" s="177"/>
+      <c r="AD16" s="177"/>
+      <c r="AE16" s="177"/>
+      <c r="AF16" s="177"/>
+      <c r="AG16" s="177"/>
+      <c r="AH16" s="179" t="inlineStr">
         <is>
           <t xml:space="preserve">source: 037 SWE1-SRA-SECURITY-SWDL-004 Requirement Description and Verification Criteria
 sibling axis: input range; rule 1 of SEC-04 4.2

--- a/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SwdlSecureLib_20260917.xlsx
+++ b/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SwdlSecureLib_20260917.xlsx
@@ -8001,7 +8001,70 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-001</t>
+          <t xml:space="preserve">CFTS084-134520
+CFTS084-134521
+CFTS084-134522
+CFTS084-134523
+CFTS084-134524
+CFTS084-134525
+CFTS084-134526
+CFTS084-134529
+CFTS084-134531
+CFTS084-134532
+CFTS084-134533
+CFTS084-134534
+CFTS084-134535
+CFTS084-134536
+CFTS084-134537
+CFTS084-134538
+CFTS084-134539
+CFTS084-134541
+CFTS084-134542
+CFTS084-134543
+CFTS084-134565
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134584
+CFTS084-134585
+CFTS084-134586
+CFTS084-134587
+CFTS084-134588
+CFTS084-134589
+CFTS084-134590
+CFTS084-134591
+CFTS084-134592
+CFTS084-134593
+CFTS084-134595
+CFTS084-134596
+CFTS084-134597
+CFTS084-134598
+CFTS084-134599
+CFTS084-134600
+CFTS084-134601
+CFTS084-134602
+CFTS084-134603
+CFTS084-134604
+CFTS084-134605
+CFTS084-134607
+CFTS084-134608
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613
+CFTS084-134804
+CFTS084-134823
+CFTS084-134824
+CFTS084-134825
+CFTS084-134827
+CFTS084-134828
+CFTS084-134841
+CFTS084-134849</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8139,7 +8202,70 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-001</t>
+          <t xml:space="preserve">CFTS084-134520
+CFTS084-134521
+CFTS084-134522
+CFTS084-134523
+CFTS084-134524
+CFTS084-134525
+CFTS084-134526
+CFTS084-134529
+CFTS084-134531
+CFTS084-134532
+CFTS084-134533
+CFTS084-134534
+CFTS084-134535
+CFTS084-134536
+CFTS084-134537
+CFTS084-134538
+CFTS084-134539
+CFTS084-134541
+CFTS084-134542
+CFTS084-134543
+CFTS084-134565
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134584
+CFTS084-134585
+CFTS084-134586
+CFTS084-134587
+CFTS084-134588
+CFTS084-134589
+CFTS084-134590
+CFTS084-134591
+CFTS084-134592
+CFTS084-134593
+CFTS084-134595
+CFTS084-134596
+CFTS084-134597
+CFTS084-134598
+CFTS084-134599
+CFTS084-134600
+CFTS084-134601
+CFTS084-134602
+CFTS084-134603
+CFTS084-134604
+CFTS084-134605
+CFTS084-134607
+CFTS084-134608
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613
+CFTS084-134804
+CFTS084-134823
+CFTS084-134824
+CFTS084-134825
+CFTS084-134827
+CFTS084-134828
+CFTS084-134841
+CFTS084-134849</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8277,7 +8403,16 @@
       </c>
       <c r="N12" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-002</t>
+          <t xml:space="preserve">CFTS084-134565
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582</t>
         </is>
       </c>
       <c r="O12" s="81" t="inlineStr">
@@ -8415,7 +8550,21 @@
       </c>
       <c r="N13" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-003</t>
+          <t xml:space="preserve">CFTS084-134531
+CFTS084-134534
+CFTS084-134535
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613</t>
         </is>
       </c>
       <c r="O13" s="177" t="inlineStr">
@@ -8554,7 +8703,21 @@
       </c>
       <c r="N14" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-003</t>
+          <t xml:space="preserve">CFTS084-134531
+CFTS084-134534
+CFTS084-134535
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613</t>
         </is>
       </c>
       <c r="O14" s="177" t="inlineStr">
@@ -8693,7 +8856,21 @@
       </c>
       <c r="N15" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-003</t>
+          <t xml:space="preserve">CFTS084-134531
+CFTS084-134534
+CFTS084-134535
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613</t>
         </is>
       </c>
       <c r="O15" s="177" t="inlineStr">
@@ -8832,7 +9009,19 @@
       </c>
       <c r="N16" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-004</t>
+          <t xml:space="preserve">CFTS084-134531
+CFTS084-134534
+CFTS084-134535
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613</t>
         </is>
       </c>
       <c r="O16" s="177" t="inlineStr">
@@ -8971,7 +9160,19 @@
       </c>
       <c r="N17" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-004</t>
+          <t xml:space="preserve">CFTS084-134531
+CFTS084-134534
+CFTS084-134535
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613</t>
         </is>
       </c>
       <c r="O17" s="81" t="inlineStr">
@@ -9109,7 +9310,19 @@
       </c>
       <c r="N18" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-004</t>
+          <t xml:space="preserve">CFTS084-134531
+CFTS084-134534
+CFTS084-134535
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613</t>
         </is>
       </c>
       <c r="O18" s="81" t="inlineStr">
@@ -9247,7 +9460,16 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-005</t>
+          <t xml:space="preserve">CFTS084-134565
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9385,7 +9607,16 @@
       </c>
       <c r="N20" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-005</t>
+          <t xml:space="preserve">CFTS084-134565
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582</t>
         </is>
       </c>
       <c r="O20" s="81" t="inlineStr">

--- a/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SwdlSecureLib_20260917.xlsx
+++ b/features/security/sandbox/delivery/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SwdlSecureLib_20260917.xlsx
@@ -8001,70 +8001,70 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134520
-CFTS084-134521
-CFTS084-134522
-CFTS084-134523
-CFTS084-134524
-CFTS084-134525
-CFTS084-134526
-CFTS084-134529
-CFTS084-134531
-CFTS084-134532
-CFTS084-134533
-CFTS084-134534
-CFTS084-134535
-CFTS084-134536
-CFTS084-134537
-CFTS084-134538
-CFTS084-134539
-CFTS084-134541
-CFTS084-134542
-CFTS084-134543
-CFTS084-134565
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134584
-CFTS084-134585
-CFTS084-134586
-CFTS084-134587
-CFTS084-134588
-CFTS084-134589
-CFTS084-134590
-CFTS084-134591
-CFTS084-134592
-CFTS084-134593
-CFTS084-134595
-CFTS084-134596
-CFTS084-134597
-CFTS084-134598
-CFTS084-134599
-CFTS084-134600
-CFTS084-134601
-CFTS084-134602
-CFTS084-134603
-CFTS084-134604
-CFTS084-134605
-CFTS084-134607
-CFTS084-134608
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613
-CFTS084-134804
-CFTS084-134823
-CFTS084-134824
-CFTS084-134825
-CFTS084-134827
-CFTS084-134828
-CFTS084-134841
-CFTS084-134849</t>
+          <t xml:space="preserve">CFTS084-4949510
+CFTS084-4949511
+CFTS084-4949512
+CFTS084-4949513
+CFTS084-4949516
+CFTS084-4949521
+CFTS084-4949522
+CFTS084-4949529
+CFTS084-4949531
+CFTS084-4949532
+CFTS084-4949533
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949538
+CFTS084-4949540
+CFTS084-4949541
+CFTS084-4949542
+CFTS084-4949545
+CFTS084-4949546
+CFTS084-4949547
+CFTS084-4949587
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949614
+CFTS084-4949615
+CFTS084-4949617
+CFTS084-4949618
+CFTS084-4949619
+CFTS084-4949620
+CFTS084-4949621
+CFTS084-4949622
+CFTS084-4949623
+CFTS084-4949624
+CFTS084-4949627
+CFTS084-4949628
+CFTS084-4949629
+CFTS084-4949630
+CFTS084-4949631
+CFTS084-4949632
+CFTS084-4949633
+CFTS084-4949634
+CFTS084-4949635
+CFTS084-4949636
+CFTS084-4949637
+CFTS084-4949639
+CFTS084-4949640
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646
+CFTS084-4949853
+CFTS084-4949878
+CFTS084-4949879
+CFTS084-4949880
+CFTS084-4949882
+CFTS084-4949883
+CFTS084-4949896
+CFTS084-4949905</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8202,70 +8202,70 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134520
-CFTS084-134521
-CFTS084-134522
-CFTS084-134523
-CFTS084-134524
-CFTS084-134525
-CFTS084-134526
-CFTS084-134529
-CFTS084-134531
-CFTS084-134532
-CFTS084-134533
-CFTS084-134534
-CFTS084-134535
-CFTS084-134536
-CFTS084-134537
-CFTS084-134538
-CFTS084-134539
-CFTS084-134541
-CFTS084-134542
-CFTS084-134543
-CFTS084-134565
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134584
-CFTS084-134585
-CFTS084-134586
-CFTS084-134587
-CFTS084-134588
-CFTS084-134589
-CFTS084-134590
-CFTS084-134591
-CFTS084-134592
-CFTS084-134593
-CFTS084-134595
-CFTS084-134596
-CFTS084-134597
-CFTS084-134598
-CFTS084-134599
-CFTS084-134600
-CFTS084-134601
-CFTS084-134602
-CFTS084-134603
-CFTS084-134604
-CFTS084-134605
-CFTS084-134607
-CFTS084-134608
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613
-CFTS084-134804
-CFTS084-134823
-CFTS084-134824
-CFTS084-134825
-CFTS084-134827
-CFTS084-134828
-CFTS084-134841
-CFTS084-134849</t>
+          <t xml:space="preserve">CFTS084-4949510
+CFTS084-4949511
+CFTS084-4949512
+CFTS084-4949513
+CFTS084-4949516
+CFTS084-4949521
+CFTS084-4949522
+CFTS084-4949529
+CFTS084-4949531
+CFTS084-4949532
+CFTS084-4949533
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949538
+CFTS084-4949540
+CFTS084-4949541
+CFTS084-4949542
+CFTS084-4949545
+CFTS084-4949546
+CFTS084-4949547
+CFTS084-4949587
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949614
+CFTS084-4949615
+CFTS084-4949617
+CFTS084-4949618
+CFTS084-4949619
+CFTS084-4949620
+CFTS084-4949621
+CFTS084-4949622
+CFTS084-4949623
+CFTS084-4949624
+CFTS084-4949627
+CFTS084-4949628
+CFTS084-4949629
+CFTS084-4949630
+CFTS084-4949631
+CFTS084-4949632
+CFTS084-4949633
+CFTS084-4949634
+CFTS084-4949635
+CFTS084-4949636
+CFTS084-4949637
+CFTS084-4949639
+CFTS084-4949640
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646
+CFTS084-4949853
+CFTS084-4949878
+CFTS084-4949879
+CFTS084-4949880
+CFTS084-4949882
+CFTS084-4949883
+CFTS084-4949896
+CFTS084-4949905</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8403,16 +8403,16 @@
       </c>
       <c r="N12" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134565
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582</t>
+          <t xml:space="preserve">CFTS084-4949587
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611</t>
         </is>
       </c>
       <c r="O12" s="81" t="inlineStr">
@@ -8550,21 +8550,21 @@
       </c>
       <c r="N13" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134531
-CFTS084-134534
-CFTS084-134535
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613</t>
+          <t xml:space="preserve">CFTS084-4949531
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646</t>
         </is>
       </c>
       <c r="O13" s="177" t="inlineStr">
@@ -8703,21 +8703,21 @@
       </c>
       <c r="N14" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134531
-CFTS084-134534
-CFTS084-134535
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613</t>
+          <t xml:space="preserve">CFTS084-4949531
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646</t>
         </is>
       </c>
       <c r="O14" s="177" t="inlineStr">
@@ -8856,21 +8856,21 @@
       </c>
       <c r="N15" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134531
-CFTS084-134534
-CFTS084-134535
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613</t>
+          <t xml:space="preserve">CFTS084-4949531
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646</t>
         </is>
       </c>
       <c r="O15" s="177" t="inlineStr">
@@ -9009,19 +9009,19 @@
       </c>
       <c r="N16" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134531
-CFTS084-134534
-CFTS084-134535
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613</t>
+          <t xml:space="preserve">CFTS084-4949531
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646</t>
         </is>
       </c>
       <c r="O16" s="177" t="inlineStr">
@@ -9160,19 +9160,19 @@
       </c>
       <c r="N17" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134531
-CFTS084-134534
-CFTS084-134535
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613</t>
+          <t xml:space="preserve">CFTS084-4949531
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646</t>
         </is>
       </c>
       <c r="O17" s="81" t="inlineStr">
@@ -9310,19 +9310,19 @@
       </c>
       <c r="N18" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134531
-CFTS084-134534
-CFTS084-134535
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613</t>
+          <t xml:space="preserve">CFTS084-4949531
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646</t>
         </is>
       </c>
       <c r="O18" s="81" t="inlineStr">
@@ -9460,16 +9460,16 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134565
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582</t>
+          <t xml:space="preserve">CFTS084-4949587
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9607,16 +9607,16 @@
       </c>
       <c r="N20" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134565
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582</t>
+          <t xml:space="preserve">CFTS084-4949587
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611</t>
         </is>
       </c>
       <c r="O20" s="81" t="inlineStr">
